--- a/sample-data/ai-cashflow-variants/01-tiem-banh-may-som/input/02_cong_no_chi_phi.xlsx
+++ b/sample-data/ai-cashflow-variants/01-tiem-banh-may-som/input/02_cong_no_chi_phi.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đọc trước" sheetId="1" r:id="R7dadabf589d14255"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HoaDonNCC" sheetId="2" r:id="R77ecff8f750049a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đọc trước" sheetId="1" r:id="Rb32036b0c4b348f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HoaDonNCC" sheetId="2" r:id="Rf467bae91df34b56"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -565,8 +565,8 @@
       <x:c r="E5" s="30" t="n">
         <x:v>8126000</x:v>
       </x:c>
-      <x:c r="F5" s="30" t="n">
-        <x:v>46117</x:v>
+      <x:c r="F5" s="30" t="str">
+        <x:v>2026-04-05</x:v>
       </x:c>
       <x:c r="G5" s="30" t="n">
         <x:v>8126000</x:v>
@@ -601,8 +601,8 @@
       <x:c r="E6" s="31" t="n">
         <x:v>2201000</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="n">
-        <x:v>46120</x:v>
+      <x:c r="F6" s="31" t="str">
+        <x:v>2026-04-08</x:v>
       </x:c>
       <x:c r="G6" s="31" t="n">
         <x:v>2201000</x:v>
@@ -637,8 +637,8 @@
       <x:c r="E7" s="31" t="n">
         <x:v>38350000</x:v>
       </x:c>
-      <x:c r="F7" s="31" t="n">
-        <x:v>46123</x:v>
+      <x:c r="F7" s="31" t="str">
+        <x:v>2026-04-11</x:v>
       </x:c>
       <x:c r="G7" s="31" t="n">
         <x:v>38350000</x:v>
@@ -673,8 +673,8 @@
       <x:c r="E8" s="31" t="n">
         <x:v>6963000</x:v>
       </x:c>
-      <x:c r="F8" s="31" t="n">
-        <x:v>46126</x:v>
+      <x:c r="F8" s="31" t="str">
+        <x:v>2026-04-14</x:v>
       </x:c>
       <x:c r="G8" s="31" t="n">
         <x:v>6963000</x:v>
@@ -709,8 +709,8 @@
       <x:c r="E9" s="31" t="n">
         <x:v>3794000</x:v>
       </x:c>
-      <x:c r="F9" s="31" t="n">
-        <x:v>46129</x:v>
+      <x:c r="F9" s="31" t="str">
+        <x:v>2026-04-17</x:v>
       </x:c>
       <x:c r="G9" s="31" t="n">
         <x:v>3794000</x:v>
@@ -745,8 +745,8 @@
       <x:c r="E10" s="31" t="n">
         <x:v>32000000</x:v>
       </x:c>
-      <x:c r="F10" s="31" t="n">
-        <x:v>46114</x:v>
+      <x:c r="F10" s="31" t="str">
+        <x:v>2026-04-02</x:v>
       </x:c>
       <x:c r="G10" s="31" t="n">
         <x:v>32000000</x:v>
@@ -781,8 +781,8 @@
       <x:c r="E11" s="31" t="n">
         <x:v>8516000</x:v>
       </x:c>
-      <x:c r="F11" s="31" t="n">
-        <x:v>46165</x:v>
+      <x:c r="F11" s="31" t="str">
+        <x:v>2026-05-23</x:v>
       </x:c>
       <x:c r="G11" s="31" t="n">
         <x:v>8516000</x:v>
@@ -817,8 +817,8 @@
       <x:c r="E12" s="31" t="n">
         <x:v>2494000</x:v>
       </x:c>
-      <x:c r="F12" s="31" t="n">
-        <x:v>46145</x:v>
+      <x:c r="F12" s="31" t="str">
+        <x:v>2026-05-03</x:v>
       </x:c>
       <x:c r="G12" s="31" t="n">
         <x:v>2494000</x:v>
@@ -853,8 +853,8 @@
       <x:c r="E13" s="31" t="n">
         <x:v>41567000</x:v>
       </x:c>
-      <x:c r="F13" s="31" t="n">
-        <x:v>46148</x:v>
+      <x:c r="F13" s="31" t="str">
+        <x:v>2026-05-06</x:v>
       </x:c>
       <x:c r="G13" s="31" t="n">
         <x:v>41567000</x:v>
@@ -889,8 +889,8 @@
       <x:c r="E14" s="31" t="n">
         <x:v>6254000</x:v>
       </x:c>
-      <x:c r="F14" s="31" t="n">
-        <x:v>46151</x:v>
+      <x:c r="F14" s="31" t="str">
+        <x:v>2026-05-09</x:v>
       </x:c>
       <x:c r="G14" s="31" t="n">
         <x:v>6254000</x:v>
@@ -925,8 +925,8 @@
       <x:c r="E15" s="31" t="n">
         <x:v>3849000</x:v>
       </x:c>
-      <x:c r="F15" s="31" t="n">
-        <x:v>46154</x:v>
+      <x:c r="F15" s="31" t="str">
+        <x:v>2026-05-12</x:v>
       </x:c>
       <x:c r="G15" s="31" t="n">
         <x:v>3849000</x:v>
@@ -961,8 +961,8 @@
       <x:c r="E16" s="31" t="n">
         <x:v>32000000</x:v>
       </x:c>
-      <x:c r="F16" s="31" t="n">
-        <x:v>46144</x:v>
+      <x:c r="F16" s="31" t="str">
+        <x:v>2026-05-02</x:v>
       </x:c>
       <x:c r="G16" s="31" t="n">
         <x:v>32000000</x:v>
@@ -997,7 +997,7 @@
       <x:c r="E17" s="31" t="n">
         <x:v>8971000</x:v>
       </x:c>
-      <x:c r="F17" s="31"/>
+      <x:c r="F17" s="31" t="str"/>
       <x:c r="G17" s="31" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -1029,7 +1029,7 @@
       <x:c r="E18" s="31" t="n">
         <x:v>2221000</x:v>
       </x:c>
-      <x:c r="F18" s="31"/>
+      <x:c r="F18" s="31" t="str"/>
       <x:c r="G18" s="31" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -1061,8 +1061,8 @@
       <x:c r="E19" s="31" t="n">
         <x:v>39563000</x:v>
       </x:c>
-      <x:c r="F19" s="31" t="n">
-        <x:v>46197</x:v>
+      <x:c r="F19" s="31" t="str">
+        <x:v>2026-06-24</x:v>
       </x:c>
       <x:c r="G19" s="31" t="n">
         <x:v>39563000</x:v>
@@ -1097,8 +1097,8 @@
       <x:c r="E20" s="31" t="n">
         <x:v>6532000</x:v>
       </x:c>
-      <x:c r="F20" s="31" t="n">
-        <x:v>46177</x:v>
+      <x:c r="F20" s="31" t="str">
+        <x:v>2026-06-04</x:v>
       </x:c>
       <x:c r="G20" s="31" t="n">
         <x:v>6532000</x:v>
@@ -1133,8 +1133,8 @@
       <x:c r="E21" s="31" t="n">
         <x:v>4096000</x:v>
       </x:c>
-      <x:c r="F21" s="31" t="n">
-        <x:v>46180</x:v>
+      <x:c r="F21" s="31" t="str">
+        <x:v>2026-06-07</x:v>
       </x:c>
       <x:c r="G21" s="31" t="n">
         <x:v>4096000</x:v>
@@ -1169,8 +1169,8 @@
       <x:c r="E22" s="32" t="n">
         <x:v>32000000</x:v>
       </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>46175</x:v>
+      <x:c r="F22" s="32" t="str">
+        <x:v>2026-06-02</x:v>
       </x:c>
       <x:c r="G22" s="32" t="n">
         <x:v>32000000</x:v>

--- a/sample-data/ai-cashflow-variants/01-tiem-banh-may-som/input/02_cong_no_chi_phi.xlsx
+++ b/sample-data/ai-cashflow-variants/01-tiem-banh-may-som/input/02_cong_no_chi_phi.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đọc trước" sheetId="1" r:id="Rb32036b0c4b348f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HoaDonNCC" sheetId="2" r:id="Rf467bae91df34b56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đọc trước" sheetId="1" r:id="R82049fd3d4004650"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HoaDonNCC" sheetId="2" r:id="R89a9b22f5c774924"/>
   </x:sheets>
 </x:workbook>
 </file>
